--- a/SBE-Design/Datas/FormatText_格式化文本.xlsx
+++ b/SBE-Design/Datas/FormatText_格式化文本.xlsx
@@ -1387,6 +1387,8 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17" s="17">
       <c r="B17" s="15" t="inlineStr">
         <is>
@@ -1399,6 +1401,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" s="17">
       <c r="B19" s="15" t="inlineStr">
         <is>
@@ -1694,7 +1697,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>CREDITS: —</t>
+          <t>CREDITS: {0:N0}</t>
         </is>
       </c>
     </row>
